--- a/Assets/开发内容.xlsx
+++ b/Assets/开发内容.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="28570" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>1.有兵目标切换成兵，不要盯着城墙，除非没有兵了</t>
   </si>
@@ -82,6 +82,15 @@
   </si>
   <si>
     <t>黑洞吸住</t>
+  </si>
+  <si>
+    <t>英雄无敌五秒钟</t>
+  </si>
+  <si>
+    <t>封路</t>
+  </si>
+  <si>
+    <t>一击击杀</t>
   </si>
   <si>
     <t>11.技能特效重置</t>
@@ -1054,69 +1063,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="42.0176991150442" customWidth="1"/>
-    <col min="3" max="3" width="32.3982300884956" customWidth="1"/>
-    <col min="4" max="4" width="19.9203539823009" customWidth="1"/>
-    <col min="5" max="5" width="16.3362831858407" customWidth="1"/>
-    <col min="6" max="6" width="27.6194690265487" customWidth="1"/>
-    <col min="7" max="7" width="18.9203539823009" customWidth="1"/>
+    <col min="1" max="1" width="42.0181818181818" customWidth="1"/>
+    <col min="3" max="3" width="22.7272727272727" customWidth="1"/>
+    <col min="4" max="4" width="23.2727272727273" customWidth="1"/>
+    <col min="5" max="5" width="16.3363636363636" customWidth="1"/>
+    <col min="6" max="6" width="27.6181818181818" customWidth="1"/>
+    <col min="7" max="7" width="18.9181818181818" customWidth="1"/>
+    <col min="8" max="8" width="15.9090909090909" customWidth="1"/>
+    <col min="9" max="9" width="17.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="41" customHeight="1" spans="1:8">
+    <row r="1" ht="41" customHeight="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:8">
+    <row r="2" ht="36" customHeight="1" spans="1:11">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" ht="35" customHeight="1" spans="1:8">
+    <row r="3" ht="35" customHeight="1" spans="1:11">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" ht="40" customHeight="1" spans="1:8">
+    <row r="4" ht="40" customHeight="1" spans="1:11">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" ht="33" customHeight="1" spans="1:8">
+    <row r="5" ht="33" customHeight="1" spans="1:11">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:8">
+    <row r="6" ht="24" customHeight="1" spans="1:11">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" ht="33" customHeight="1" spans="1:8">
+    <row r="7" ht="33" customHeight="1" spans="1:11">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" ht="29" customHeight="1" spans="1:8">
+    <row r="9" ht="29" customHeight="1" spans="1:11">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:8">
+    <row r="10" ht="24" customHeight="1" spans="1:11">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1138,63 +1149,72 @@
       <c r="H10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" ht="29" customHeight="1" spans="1:8">
+      <c r="I10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" ht="29" customHeight="1" spans="1:11">
       <c r="A11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="C13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="C14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="C15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="C16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="3:3">
       <c r="C21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1208,7 +1228,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1220,7 +1240,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/开发内容.xlsx
+++ b/Assets/开发内容.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28570" windowHeight="12280"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>1.有兵目标切换成兵，不要盯着城墙，除非没有兵了</t>
   </si>
@@ -63,6 +63,12 @@
     <t>9.新增士兵</t>
   </si>
   <si>
+    <t>七星灯</t>
+  </si>
+  <si>
+    <t>长驱直入</t>
+  </si>
+  <si>
     <t>10.新增技能效果</t>
   </si>
   <si>
@@ -81,30 +87,42 @@
     <t>英雄复活一次</t>
   </si>
   <si>
+    <t>英雄死亡时再存活五秒钟</t>
+  </si>
+  <si>
+    <t>封路</t>
+  </si>
+  <si>
+    <t>一击击杀</t>
+  </si>
+  <si>
+    <t>英雄冲撞</t>
+  </si>
+  <si>
+    <t>传送阵</t>
+  </si>
+  <si>
+    <t>11.技能特效重置</t>
+  </si>
+  <si>
     <t>黑洞吸住</t>
   </si>
   <si>
-    <t>英雄无敌五秒钟</t>
-  </si>
-  <si>
-    <t>封路</t>
-  </si>
-  <si>
-    <t>一击击杀</t>
-  </si>
-  <si>
-    <t>11.技能特效重置</t>
-  </si>
-  <si>
     <t>12.事件</t>
   </si>
   <si>
     <t>积分点获取，胜点获取</t>
   </si>
   <si>
+    <t>时空倒转</t>
+  </si>
+  <si>
     <t>积分排行，清空</t>
   </si>
   <si>
+    <t>飞行球 贝塞尔曲线</t>
+  </si>
+  <si>
     <t>玩家 + 召唤士兵 x 数量</t>
   </si>
   <si>
@@ -127,6 +145,30 @@
   </si>
   <si>
     <t>英雄升星</t>
+  </si>
+  <si>
+    <t>13.受击效果</t>
+  </si>
+  <si>
+    <t>受击顿针，旋转飞出，落地弹地</t>
+  </si>
+  <si>
+    <t>打中钝帧 飞上高空，后仰落下</t>
+  </si>
+  <si>
+    <t>旋风旋转</t>
+  </si>
+  <si>
+    <t>已有</t>
+  </si>
+  <si>
+    <t>撞击到UI边缘</t>
+  </si>
+  <si>
+    <t>溶解死亡</t>
+  </si>
+  <si>
+    <t>打中钝帧，炸开</t>
   </si>
 </sst>
 </file>
@@ -1063,158 +1105,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="42.0181818181818" customWidth="1"/>
-    <col min="3" max="3" width="22.7272727272727" customWidth="1"/>
+    <col min="3" max="3" width="29.7363636363636" customWidth="1"/>
     <col min="4" max="4" width="23.2727272727273" customWidth="1"/>
     <col min="5" max="5" width="16.3363636363636" customWidth="1"/>
     <col min="6" max="6" width="27.6181818181818" customWidth="1"/>
     <col min="7" max="7" width="18.9181818181818" customWidth="1"/>
     <col min="8" max="8" width="15.9090909090909" customWidth="1"/>
-    <col min="9" max="9" width="17.1818181818182" customWidth="1"/>
+    <col min="9" max="9" width="34.5454545454545" customWidth="1"/>
+    <col min="10" max="10" width="35.6090909090909" customWidth="1"/>
+    <col min="11" max="11" width="14.7636363636364" customWidth="1"/>
+    <col min="12" max="12" width="24.3818181818182" customWidth="1"/>
+    <col min="13" max="13" width="25.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="41" customHeight="1" spans="1:11">
+    <row r="1" ht="41" customHeight="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:11">
+    <row r="2" ht="36" customHeight="1" spans="1:13">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" ht="35" customHeight="1" spans="1:11">
+    <row r="3" ht="35" customHeight="1" spans="1:13">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" ht="40" customHeight="1" spans="1:11">
+    <row r="4" ht="40" customHeight="1" spans="1:13">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" ht="33" customHeight="1" spans="1:11">
+    <row r="5" ht="33" customHeight="1" spans="1:13">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:11">
+    <row r="6" ht="24" customHeight="1" spans="1:13">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" ht="33" customHeight="1" spans="1:11">
+    <row r="7" ht="33" customHeight="1" spans="1:13">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" ht="29" customHeight="1" spans="1:11">
+    <row r="9" ht="29" customHeight="1" spans="1:13">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:11">
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:13">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" ht="29" customHeight="1" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="29" customHeight="1" spans="1:13">
       <c r="A11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="C13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>27</v>
+      </c>
+      <c r="M13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="C14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="C15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="C16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="C17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="C18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="C19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="C20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="C21" t="s">
-        <v>30</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="C26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="C29" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
